--- a/output/Graficos.xlsx
+++ b/output/Graficos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\espin\Desktop\Semillero_coyuntura_economica\balanza-de-pagos\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DA8B1A-B996-438E-A618-9C0C1C6E6274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3220A7AF-708B-4B3C-922E-516D554B0591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="2948" windowWidth="16200" windowHeight="8294" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen CA" sheetId="1" r:id="rId1"/>
@@ -3195,7 +3195,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8670192" cy="6288942"/>
+    <xdr:ext cx="8652993" cy="6278451"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -3228,7 +3228,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8670192" cy="6288942"/>
+    <xdr:ext cx="8652993" cy="6278451"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Gráfico 1">
